--- a/memory/testcases/NREQUEST-47453_testcases.xlsx
+++ b/memory/testcases/NREQUEST-47453_testcases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TestScheduler\memory\testcases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D18AA2C6-D8F7-4BE3-A844-FEEFF11720A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{210F2369-D918-4D60-ACCF-8EC6B729E1EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-5352" yWindow="-17388" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
